--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487949_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487949_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4115</v>
+        <v>6.7235</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2997</v>
+        <v>6.4431</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1119</v>
+        <v>0.2803</v>
       </c>
       <c r="G2" t="n">
         <v>8.074299999999999</v>
@@ -610,13 +610,13 @@
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8699</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.8719</v>
+        <v>-0.7284</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002</v>
+        <v>0.1705</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7494</v>
+        <v>3.6339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2437</v>
+        <v>1.3248</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5057</v>
+        <v>2.3092</v>
       </c>
       <c r="G3" t="n">
         <v>1.6588</v>
@@ -688,13 +688,13 @@
         <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2376</v>
+        <v>0.647</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4351</v>
+        <v>-0.354</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1976</v>
+        <v>1.001</v>
       </c>
       <c r="V3" t="n">
         <v>0.337</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2561</v>
+        <v>2.4317</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5524</v>
+        <v>1.7562</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7036</v>
+        <v>0.6756</v>
       </c>
       <c r="G4" t="n">
         <v>3.6543</v>
@@ -766,13 +766,13 @@
         <v>0.3964</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1171</v>
+        <v>0.2928</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8808</v>
+        <v>-0.6771</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9979</v>
+        <v>0.9698</v>
       </c>
       <c r="V4" t="n">
         <v>0.0704</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1064</v>
+        <v>-0.5972</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5869</v>
+        <v>0.6306</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4805</v>
+        <v>-1.2278</v>
       </c>
       <c r="G6" t="n">
         <v>0.634</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0165</v>
+        <v>0.3129</v>
       </c>
       <c r="T6" t="n">
-        <v>0.727</v>
+        <v>-0.2293</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2895</v>
+        <v>0.5422</v>
       </c>
       <c r="V6" t="n">
         <v>-1.5441</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>F. MALENO BERENGUER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.414</v>
+        <v>-1.3123</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0596</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6456</v>
+        <v>-1.2472</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.5897</v>
+        <v>-0.3117</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5378</v>
+        <v>0.0901</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0518</v>
+        <v>-0.4018</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6474</v>
+        <v>0.0202</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2897</v>
+        <v>0.0202</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3577</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0578</v>
+        <v>-0.3319</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2481</v>
+        <v>0.0699</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3059</v>
+        <v>-0.4018</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3739</v>
+        <v>0.0083</v>
       </c>
       <c r="T7" t="n">
-        <v>0.907</v>
+        <v>-0.0853</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4669</v>
+        <v>0.0936</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2071</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8701</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. MALENO BERENGUER</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4704</v>
+        <v>-1.6157</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.167</v>
+        <v>-1.7443</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3033</v>
+        <v>0.1285</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3117</v>
+        <v>1.5354</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0901</v>
+        <v>1.3612</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4018</v>
+        <v>0.1742</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0202</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0202</v>
+        <v>0.6664</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3319</v>
+        <v>0.8535</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0699</v>
+        <v>0.6948</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4018</v>
+        <v>0.1586</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1498</v>
+        <v>0.0559</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1872</v>
+        <v>-0.444</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0374</v>
+        <v>0.5</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4878</v>
+        <v>-1.9948</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8691</v>
+        <v>-2.7962</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3812</v>
+        <v>0.8014</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5354</v>
+        <v>0.263</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3612</v>
+        <v>0.0163</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1742</v>
+        <v>0.2468</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6820000000000001</v>
+        <v>-0.7673</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6664</v>
+        <v>-0.3292</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0156</v>
+        <v>-0.4381</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8535</v>
+        <v>1.0303</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6948</v>
+        <v>0.3455</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1586</v>
+        <v>0.6848</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7929</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1838</v>
+        <v>0.1386</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5688</v>
+        <v>-0.0467</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7527</v>
+        <v>0.1853</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>F. PEREGRINA FEDOTOV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1238</v>
+        <v>-2.4713</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7567</v>
+        <v>-1.0068</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6329</v>
+        <v>-1.4646</v>
       </c>
       <c r="G10" t="n">
-        <v>0.263</v>
+        <v>-0.9564</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0163</v>
+        <v>-1.0827</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2468</v>
+        <v>0.1262</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7673</v>
+        <v>-0.5586</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3292</v>
+        <v>-0.6791</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4381</v>
+        <v>0.1205</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0303</v>
+        <v>-0.3979</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3455</v>
+        <v>-0.4036</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6848</v>
+        <v>0.0057</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.3662</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0072</v>
+        <v>0.2258</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0168</v>
+        <v>0.1404</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>-1.8811</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2071</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. PEREGRINA FEDOTOV</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3518</v>
+        <v>-3.1574</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.803</v>
+        <v>-4.1573</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5488</v>
+        <v>0.9998</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9564</v>
+        <v>-1.5897</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0827</v>
+        <v>-1.5378</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1262</v>
+        <v>-0.0518</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5586</v>
+        <v>-1.6474</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6791</v>
+        <v>-1.2897</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1205</v>
+        <v>-0.3577</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3979</v>
+        <v>0.0578</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4036</v>
+        <v>-0.2481</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0057</v>
+        <v>0.3059</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4857</v>
+        <v>0.6304</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4295</v>
+        <v>-0.1906</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0562</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8811</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.674</v>
+        <v>-0.337</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.777</v>
+        <v>-5.1177</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0174</v>
+        <v>-4.7513</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7595</v>
+        <v>-0.3664</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4724</v>
@@ -1390,13 +1390,13 @@
         <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5623</v>
+        <v>-0.903</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4975</v>
+        <v>-1.2314</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.3284</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.896100000000001</v>
+        <v>-2.271999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.784800000000002</v>
+        <v>-3.161</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8888000000000008</v>
+        <v>0.8888000000000003</v>
       </c>
       <c r="G13" t="n">
         <v>10.6949</v>
@@ -1441,7 +1441,7 @@
         <v>14.7697</v>
       </c>
       <c r="J13" t="n">
-        <v>10.9892</v>
+        <v>10.98920000000001</v>
       </c>
       <c r="K13" t="n">
         <v>-2.1942</v>
@@ -1450,7 +1450,7 @@
         <v>13.1834</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2939999999999997</v>
+        <v>-0.2939999999999998</v>
       </c>
       <c r="N13" t="n">
         <v>-1.8804</v>
@@ -1459,7 +1459,7 @@
         <v>1.5863</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.9645</v>
+        <v>-3.964500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-9.911</v>
@@ -1468,13 +1468,13 @@
         <v>5.9465</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3669999999999995</v>
+        <v>0.9910999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.385</v>
+        <v>-3.761</v>
       </c>
       <c r="U13" t="n">
-        <v>4.752299999999999</v>
+        <v>4.752300000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-9.9938</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.6284</v>
+        <v>12.3498</v>
       </c>
       <c r="E14" t="n">
-        <v>10.989</v>
+        <v>9.7666</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6393</v>
+        <v>2.5832</v>
       </c>
       <c r="G14" t="n">
         <v>6.723</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7686</v>
+        <v>0.49</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7198</v>
+        <v>-0.5026</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0488</v>
+        <v>0.9927</v>
       </c>
       <c r="V14" t="n">
         <v>3.5509</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4612</v>
+        <v>2.4706</v>
       </c>
       <c r="E15" t="n">
-        <v>4.894</v>
+        <v>3.8753</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4328</v>
+        <v>-1.4047</v>
       </c>
       <c r="G15" t="n">
         <v>0.2493</v>
@@ -1624,13 +1624,13 @@
         <v>0.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2119</v>
+        <v>0.2212</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9142</v>
+        <v>-0.1045</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2976</v>
+        <v>0.3257</v>
       </c>
       <c r="V15" t="n">
         <v>1.2071</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7713</v>
+        <v>0.8592</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4977</v>
+        <v>-2.1319</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2689</v>
+        <v>2.9911</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5147</v>
+        <v>0.1453</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0414</v>
+        <v>2.2057</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5561</v>
+        <v>-2.0605</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1892</v>
+        <v>-0.648</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.876</v>
+        <v>1.3052</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0652</v>
+        <v>-1.9531</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3255</v>
+        <v>0.7932</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8346</v>
+        <v>0.9005</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5091</v>
+        <v>-0.1073</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2477</v>
+        <v>-0.4754</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5064</v>
+        <v>-0.9487</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7541</v>
+        <v>0.4733</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ GUZMÁN</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6027</v>
+        <v>0.6309</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6027</v>
+        <v>-1.4977</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.1285</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6027</v>
+        <v>1.5147</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1.0414</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6027</v>
+        <v>2.5561</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6027</v>
+        <v>1.1892</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-1.876</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6027</v>
+        <v>3.0652</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.3255</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.8346</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.5091</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1805</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1073</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5064</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.6137</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. MARTÍNEZ GUZMÁN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,31 +1813,31 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1357</v>
+        <v>0.3027</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7431</v>
+        <v>0.3027</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8788</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1453</v>
+        <v>0.3027</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2057</v>
+        <v>0.3027</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0605</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.648</v>
+        <v>0.3027</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3052</v>
+        <v>0.3027</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9531</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7932</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9005</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1073</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1989</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5599</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7703</v>
+        <v>-0.6123</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4635</v>
+        <v>0.5654</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2338</v>
+        <v>-1.1777</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8901</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0707</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V20" t="n">
         <v>1.2071</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6231</v>
+        <v>-0.8815</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6768</v>
+        <v>-2.627</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0537</v>
+        <v>1.7455</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6399</v>
+        <v>-4.8543</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7101</v>
+        <v>-0.4695</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9298</v>
+        <v>-4.3848</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4802</v>
+        <v>-3.7919</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3312</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.149</v>
+        <v>-2.8176</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1597</v>
+        <v>-1.0624</v>
       </c>
       <c r="N21" t="n">
-        <v>0.621</v>
+        <v>0.5048</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.5672</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7929</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5778</v>
+        <v>-0.4414</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9984</v>
+        <v>-1.2671</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4205</v>
+        <v>0.8256</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3.6213</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6213</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9107</v>
+        <v>-1.4298</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5439</v>
+        <v>-2.3712</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6332</v>
+        <v>0.9414</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.8543</v>
+        <v>-1.6399</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4695</v>
+        <v>-0.7101</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.3848</v>
+        <v>-0.9298</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7919</v>
+        <v>-1.4802</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-1.3312</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.8176</v>
+        <v>-0.149</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0624</v>
+        <v>-0.1597</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5048</v>
+        <v>0.621</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5672</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P22" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.1982</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.7929</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.1893</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.9822</v>
-      </c>
       <c r="S22" t="n">
-        <v>-1.4706</v>
+        <v>-0.3846</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.1839</v>
+        <v>-0.6927</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7133</v>
+        <v>0.3082</v>
       </c>
       <c r="V22" t="n">
-        <v>3.6213</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.6213</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2856</v>
+        <v>-2.2118</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3481</v>
+        <v>-3.2463</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0626</v>
+        <v>1.0345</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9943</v>
@@ -2248,13 +2248,13 @@
         <v>0.7929</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2419</v>
+        <v>0.3157</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1944</v>
+        <v>-0.0926</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4363</v>
+        <v>0.4083</v>
       </c>
       <c r="V23" t="n">
         <v>0.674</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.766</v>
+        <v>-2.5799</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2113</v>
+        <v>-0.1094</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5548</v>
+        <v>-2.4705</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1702</v>
@@ -2326,13 +2326,13 @@
         <v>0.1982</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5275</v>
+        <v>-0.3414</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.312</v>
+        <v>-0.2101</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2666</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9327</v>
+        <v>-2.8413</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5449</v>
+        <v>-2.3412</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3878</v>
+        <v>-0.5001</v>
       </c>
       <c r="G25" t="n">
         <v>-2.3145</v>
@@ -2404,13 +2404,13 @@
         <v>0.3964</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0235</v>
+        <v>0.0679</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4133</v>
+        <v>0.301</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.7174</v>
+        <v>-3.7631</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.5749</v>
+        <v>-1.6768</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.1424</v>
+        <v>-2.0863</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3694</v>
@@ -2482,13 +2482,13 @@
         <v>0.5947</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0485</v>
+        <v>0.0028</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1181</v>
+        <v>0.1743</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2518,10 +2518,10 @@
         <v>2.896199999999996</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8887999999999994</v>
+        <v>-0.8888000000000007</v>
       </c>
       <c r="F27" t="n">
-        <v>3.784899999999999</v>
+        <v>3.7849</v>
       </c>
       <c r="G27" t="n">
         <v>-10.695</v>
@@ -2536,10 +2536,10 @@
         <v>0.2940999999999989</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8803</v>
+        <v>1.880299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.586200000000001</v>
+        <v>-1.5862</v>
       </c>
       <c r="M27" t="n">
         <v>-10.9891</v>
@@ -2560,16 +2560,16 @@
         <v>9.911099999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3670999999999998</v>
+        <v>-0.3671999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.7522</v>
+        <v>-4.7521</v>
       </c>
       <c r="U27" t="n">
-        <v>4.384900000000001</v>
+        <v>4.3851</v>
       </c>
       <c r="V27" t="n">
-        <v>9.993799999999998</v>
+        <v>9.9938</v>
       </c>
       <c r="W27" t="n">
         <v>9.516</v>
